--- a/selenium_tests/SkillSync_E2E_Test_Report.xlsx
+++ b/selenium_tests/SkillSync_E2E_Test_Report.xlsx
@@ -27,7 +27,7 @@
     <t>Test Execution Timestamp</t>
   </si>
   <si>
-    <t>17/8/2026, 12:37:46 pm</t>
+    <t>17/8/2026, 2:13:49 pm</t>
   </si>
   <si>
     <t>Total Load Test Scenarios</t>
@@ -21053,7 +21053,7 @@
         <v>1089</v>
       </c>
       <c r="G2" s="13">
-        <v>96</v>
+        <v>63</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -21076,7 +21076,7 @@
         <v>1089</v>
       </c>
       <c r="G3" s="13">
-        <v>76</v>
+        <v>37</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -21099,7 +21099,7 @@
         <v>1089</v>
       </c>
       <c r="G4" s="13">
-        <v>46</v>
+        <v>56</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -21122,7 +21122,7 @@
         <v>1089</v>
       </c>
       <c r="G5" s="13">
-        <v>96</v>
+        <v>77</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -21145,7 +21145,7 @@
         <v>1089</v>
       </c>
       <c r="G6" s="13">
-        <v>96</v>
+        <v>59</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -21168,7 +21168,7 @@
         <v>1089</v>
       </c>
       <c r="G7" s="13">
-        <v>86</v>
+        <v>39</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -21191,7 +21191,7 @@
         <v>1089</v>
       </c>
       <c r="G8" s="13">
-        <v>49</v>
+        <v>81</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -21214,7 +21214,7 @@
         <v>1089</v>
       </c>
       <c r="G9" s="13">
-        <v>35</v>
+        <v>74</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -21237,7 +21237,7 @@
         <v>1089</v>
       </c>
       <c r="G10" s="13">
-        <v>46</v>
+        <v>81</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -21260,7 +21260,7 @@
         <v>1089</v>
       </c>
       <c r="G11" s="13">
-        <v>56</v>
+        <v>81</v>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -21283,7 +21283,7 @@
         <v>1089</v>
       </c>
       <c r="G12" s="13">
-        <v>69</v>
+        <v>49</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -21306,7 +21306,7 @@
         <v>1089</v>
       </c>
       <c r="G13" s="13">
-        <v>87</v>
+        <v>91</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -21329,7 +21329,7 @@
         <v>1089</v>
       </c>
       <c r="G14" s="13">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -21352,7 +21352,7 @@
         <v>1089</v>
       </c>
       <c r="G15" s="13">
-        <v>59</v>
+        <v>77</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -21375,7 +21375,7 @@
         <v>1089</v>
       </c>
       <c r="G16" s="13">
-        <v>55</v>
+        <v>67</v>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -21398,7 +21398,7 @@
         <v>1089</v>
       </c>
       <c r="G17" s="13">
-        <v>48</v>
+        <v>81</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -21421,7 +21421,7 @@
         <v>1089</v>
       </c>
       <c r="G18" s="13">
-        <v>58</v>
+        <v>65</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -21444,7 +21444,7 @@
         <v>1089</v>
       </c>
       <c r="G19" s="13">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -21467,7 +21467,7 @@
         <v>1089</v>
       </c>
       <c r="G20" s="13">
-        <v>61</v>
+        <v>65</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -21490,7 +21490,7 @@
         <v>1089</v>
       </c>
       <c r="G21" s="13">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="22" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -21513,7 +21513,7 @@
         <v>1089</v>
       </c>
       <c r="G22" s="13">
-        <v>75</v>
+        <v>92</v>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -21536,7 +21536,7 @@
         <v>1089</v>
       </c>
       <c r="G23" s="13">
-        <v>78</v>
+        <v>42</v>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -21559,7 +21559,7 @@
         <v>1089</v>
       </c>
       <c r="G24" s="13">
-        <v>89</v>
+        <v>78</v>
       </c>
     </row>
     <row r="25" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -21582,7 +21582,7 @@
         <v>1089</v>
       </c>
       <c r="G25" s="13">
-        <v>70</v>
+        <v>50</v>
       </c>
     </row>
     <row r="26" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -21605,7 +21605,7 @@
         <v>1089</v>
       </c>
       <c r="G26" s="13">
-        <v>92</v>
+        <v>39</v>
       </c>
     </row>
     <row r="27" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -21628,7 +21628,7 @@
         <v>1089</v>
       </c>
       <c r="G27" s="13">
-        <v>62</v>
+        <v>45</v>
       </c>
     </row>
     <row r="28" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -21651,7 +21651,7 @@
         <v>1089</v>
       </c>
       <c r="G28" s="13">
-        <v>54</v>
+        <v>62</v>
       </c>
     </row>
     <row r="29" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -21674,7 +21674,7 @@
         <v>1089</v>
       </c>
       <c r="G29" s="13">
-        <v>95</v>
+        <v>48</v>
       </c>
     </row>
     <row r="30" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -21697,7 +21697,7 @@
         <v>1089</v>
       </c>
       <c r="G30" s="13">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="31" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -21720,7 +21720,7 @@
         <v>1089</v>
       </c>
       <c r="G31" s="13">
-        <v>49</v>
+        <v>57</v>
       </c>
     </row>
     <row r="32" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -21743,7 +21743,7 @@
         <v>1089</v>
       </c>
       <c r="G32" s="13">
-        <v>83</v>
+        <v>54</v>
       </c>
     </row>
     <row r="33" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -21766,7 +21766,7 @@
         <v>1089</v>
       </c>
       <c r="G33" s="13">
-        <v>82</v>
+        <v>47</v>
       </c>
     </row>
     <row r="34" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -21789,7 +21789,7 @@
         <v>1089</v>
       </c>
       <c r="G34" s="13">
-        <v>48</v>
+        <v>51</v>
       </c>
     </row>
     <row r="35" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -21812,7 +21812,7 @@
         <v>1089</v>
       </c>
       <c r="G35" s="13">
-        <v>48</v>
+        <v>67</v>
       </c>
     </row>
     <row r="36" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -21835,7 +21835,7 @@
         <v>1089</v>
       </c>
       <c r="G36" s="13">
-        <v>73</v>
+        <v>35</v>
       </c>
     </row>
     <row r="37" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -21858,7 +21858,7 @@
         <v>1089</v>
       </c>
       <c r="G37" s="13">
-        <v>52</v>
+        <v>67</v>
       </c>
     </row>
     <row r="38" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -21881,7 +21881,7 @@
         <v>1089</v>
       </c>
       <c r="G38" s="13">
-        <v>53</v>
+        <v>62</v>
       </c>
     </row>
     <row r="39" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -21904,7 +21904,7 @@
         <v>1089</v>
       </c>
       <c r="G39" s="13">
-        <v>35</v>
+        <v>60</v>
       </c>
     </row>
     <row r="40" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -21927,7 +21927,7 @@
         <v>1089</v>
       </c>
       <c r="G40" s="13">
-        <v>39</v>
+        <v>73</v>
       </c>
     </row>
     <row r="41" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -21950,7 +21950,7 @@
         <v>1089</v>
       </c>
       <c r="G41" s="13">
-        <v>78</v>
+        <v>54</v>
       </c>
     </row>
     <row r="42" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -21973,7 +21973,7 @@
         <v>1089</v>
       </c>
       <c r="G42" s="13">
-        <v>47</v>
+        <v>43</v>
       </c>
     </row>
     <row r="43" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -21996,7 +21996,7 @@
         <v>1089</v>
       </c>
       <c r="G43" s="13">
-        <v>36</v>
+        <v>83</v>
       </c>
     </row>
     <row r="44" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -22019,7 +22019,7 @@
         <v>1089</v>
       </c>
       <c r="G44" s="13">
-        <v>58</v>
+        <v>78</v>
       </c>
     </row>
     <row r="45" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -22042,7 +22042,7 @@
         <v>1089</v>
       </c>
       <c r="G45" s="13">
-        <v>81</v>
+        <v>74</v>
       </c>
     </row>
     <row r="46" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -22065,7 +22065,7 @@
         <v>1089</v>
       </c>
       <c r="G46" s="13">
-        <v>57</v>
+        <v>43</v>
       </c>
     </row>
     <row r="47" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -22088,7 +22088,7 @@
         <v>1089</v>
       </c>
       <c r="G47" s="13">
-        <v>78</v>
+        <v>49</v>
       </c>
     </row>
     <row r="48" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -22111,7 +22111,7 @@
         <v>1089</v>
       </c>
       <c r="G48" s="13">
-        <v>64</v>
+        <v>85</v>
       </c>
     </row>
     <row r="49" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -22134,7 +22134,7 @@
         <v>1089</v>
       </c>
       <c r="G49" s="13">
-        <v>55</v>
+        <v>68</v>
       </c>
     </row>
     <row r="50" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -22157,7 +22157,7 @@
         <v>1089</v>
       </c>
       <c r="G50" s="13">
-        <v>65</v>
+        <v>51</v>
       </c>
     </row>
     <row r="51" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -22180,7 +22180,7 @@
         <v>1089</v>
       </c>
       <c r="G51" s="13">
-        <v>66</v>
+        <v>81</v>
       </c>
     </row>
     <row r="52" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -22203,7 +22203,7 @@
         <v>1089</v>
       </c>
       <c r="G52" s="13">
-        <v>84</v>
+        <v>41</v>
       </c>
     </row>
     <row r="53" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -22226,7 +22226,7 @@
         <v>1089</v>
       </c>
       <c r="G53" s="13">
-        <v>84</v>
+        <v>51</v>
       </c>
     </row>
     <row r="54" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -22249,7 +22249,7 @@
         <v>1089</v>
       </c>
       <c r="G54" s="13">
-        <v>71</v>
+        <v>86</v>
       </c>
     </row>
     <row r="55" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -22272,7 +22272,7 @@
         <v>1089</v>
       </c>
       <c r="G55" s="13">
-        <v>89</v>
+        <v>93</v>
       </c>
     </row>
     <row r="56" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -22295,7 +22295,7 @@
         <v>1089</v>
       </c>
       <c r="G56" s="13">
-        <v>45</v>
+        <v>60</v>
       </c>
     </row>
     <row r="57" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -22318,7 +22318,7 @@
         <v>1089</v>
       </c>
       <c r="G57" s="13">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="58" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -22341,7 +22341,7 @@
         <v>1089</v>
       </c>
       <c r="G58" s="13">
-        <v>61</v>
+        <v>89</v>
       </c>
     </row>
     <row r="59" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -22364,7 +22364,7 @@
         <v>1089</v>
       </c>
       <c r="G59" s="13">
-        <v>55</v>
+        <v>82</v>
       </c>
     </row>
     <row r="60" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -22387,7 +22387,7 @@
         <v>1089</v>
       </c>
       <c r="G60" s="13">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="61" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -22410,7 +22410,7 @@
         <v>1089</v>
       </c>
       <c r="G61" s="13">
-        <v>73</v>
+        <v>54</v>
       </c>
     </row>
     <row r="62" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -22433,7 +22433,7 @@
         <v>1089</v>
       </c>
       <c r="G62" s="13">
-        <v>74</v>
+        <v>85</v>
       </c>
     </row>
     <row r="63" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -22456,7 +22456,7 @@
         <v>1089</v>
       </c>
       <c r="G63" s="13">
-        <v>73</v>
+        <v>90</v>
       </c>
     </row>
     <row r="64" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -22479,7 +22479,7 @@
         <v>1089</v>
       </c>
       <c r="G64" s="13">
-        <v>46</v>
+        <v>89</v>
       </c>
     </row>
     <row r="65" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -22502,7 +22502,7 @@
         <v>1089</v>
       </c>
       <c r="G65" s="13">
-        <v>99</v>
+        <v>76</v>
       </c>
     </row>
     <row r="66" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -22525,7 +22525,7 @@
         <v>1089</v>
       </c>
       <c r="G66" s="13">
-        <v>86</v>
+        <v>95</v>
       </c>
     </row>
     <row r="67" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -22548,7 +22548,7 @@
         <v>1089</v>
       </c>
       <c r="G67" s="13">
-        <v>61</v>
+        <v>97</v>
       </c>
     </row>
     <row r="68" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -22571,7 +22571,7 @@
         <v>1089</v>
       </c>
       <c r="G68" s="13">
-        <v>56</v>
+        <v>37</v>
       </c>
     </row>
     <row r="69" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -22594,7 +22594,7 @@
         <v>1089</v>
       </c>
       <c r="G69" s="13">
-        <v>98</v>
+        <v>42</v>
       </c>
     </row>
     <row r="70" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -22617,7 +22617,7 @@
         <v>1089</v>
       </c>
       <c r="G70" s="13">
-        <v>61</v>
+        <v>43</v>
       </c>
     </row>
     <row r="71" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -22640,7 +22640,7 @@
         <v>1089</v>
       </c>
       <c r="G71" s="13">
-        <v>54</v>
+        <v>61</v>
       </c>
     </row>
     <row r="72" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -22663,7 +22663,7 @@
         <v>1089</v>
       </c>
       <c r="G72" s="13">
-        <v>69</v>
+        <v>97</v>
       </c>
     </row>
     <row r="73" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -22686,7 +22686,7 @@
         <v>1089</v>
       </c>
       <c r="G73" s="13">
-        <v>53</v>
+        <v>66</v>
       </c>
     </row>
     <row r="74" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -22709,7 +22709,7 @@
         <v>1089</v>
       </c>
       <c r="G74" s="13">
-        <v>43</v>
+        <v>82</v>
       </c>
     </row>
     <row r="75" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -22732,7 +22732,7 @@
         <v>1089</v>
       </c>
       <c r="G75" s="13">
-        <v>40</v>
+        <v>85</v>
       </c>
     </row>
     <row r="76" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -22755,7 +22755,7 @@
         <v>1089</v>
       </c>
       <c r="G76" s="13">
-        <v>83</v>
+        <v>95</v>
       </c>
     </row>
     <row r="77" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -22778,7 +22778,7 @@
         <v>1089</v>
       </c>
       <c r="G77" s="13">
-        <v>80</v>
+        <v>42</v>
       </c>
     </row>
     <row r="78" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -22801,7 +22801,7 @@
         <v>1089</v>
       </c>
       <c r="G78" s="13">
-        <v>70</v>
+        <v>74</v>
       </c>
     </row>
     <row r="79" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -22824,7 +22824,7 @@
         <v>1089</v>
       </c>
       <c r="G79" s="13">
-        <v>63</v>
+        <v>38</v>
       </c>
     </row>
     <row r="80" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -22847,7 +22847,7 @@
         <v>1089</v>
       </c>
       <c r="G80" s="13">
-        <v>66</v>
+        <v>93</v>
       </c>
     </row>
     <row r="81" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -22870,7 +22870,7 @@
         <v>1089</v>
       </c>
       <c r="G81" s="13">
-        <v>36</v>
+        <v>42</v>
       </c>
     </row>
     <row r="82" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -22893,7 +22893,7 @@
         <v>1089</v>
       </c>
       <c r="G82" s="13">
-        <v>39</v>
+        <v>66</v>
       </c>
     </row>
     <row r="83" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -22916,7 +22916,7 @@
         <v>1089</v>
       </c>
       <c r="G83" s="13">
-        <v>98</v>
+        <v>88</v>
       </c>
     </row>
     <row r="84" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -22939,7 +22939,7 @@
         <v>1089</v>
       </c>
       <c r="G84" s="13">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="85" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -22962,7 +22962,7 @@
         <v>1089</v>
       </c>
       <c r="G85" s="13">
-        <v>43</v>
+        <v>74</v>
       </c>
     </row>
     <row r="86" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -22985,7 +22985,7 @@
         <v>1089</v>
       </c>
       <c r="G86" s="13">
-        <v>35</v>
+        <v>60</v>
       </c>
     </row>
     <row r="87" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -23008,7 +23008,7 @@
         <v>1089</v>
       </c>
       <c r="G87" s="13">
-        <v>91</v>
+        <v>53</v>
       </c>
     </row>
     <row r="88" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -23031,7 +23031,7 @@
         <v>1089</v>
       </c>
       <c r="G88" s="13">
-        <v>75</v>
+        <v>37</v>
       </c>
     </row>
     <row r="89" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -23054,7 +23054,7 @@
         <v>1089</v>
       </c>
       <c r="G89" s="13">
-        <v>49</v>
+        <v>85</v>
       </c>
     </row>
     <row r="90" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -23077,7 +23077,7 @@
         <v>1089</v>
       </c>
       <c r="G90" s="13">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="91" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -23100,7 +23100,7 @@
         <v>1089</v>
       </c>
       <c r="G91" s="13">
-        <v>89</v>
+        <v>74</v>
       </c>
     </row>
     <row r="92" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -23123,7 +23123,7 @@
         <v>1089</v>
       </c>
       <c r="G92" s="13">
-        <v>90</v>
+        <v>38</v>
       </c>
     </row>
     <row r="93" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -23146,7 +23146,7 @@
         <v>1089</v>
       </c>
       <c r="G93" s="13">
-        <v>54</v>
+        <v>64</v>
       </c>
     </row>
     <row r="94" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -23169,7 +23169,7 @@
         <v>1089</v>
       </c>
       <c r="G94" s="13">
-        <v>57</v>
+        <v>96</v>
       </c>
     </row>
     <row r="95" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -23192,7 +23192,7 @@
         <v>1089</v>
       </c>
       <c r="G95" s="13">
-        <v>42</v>
+        <v>76</v>
       </c>
     </row>
     <row r="96" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -23215,7 +23215,7 @@
         <v>1089</v>
       </c>
       <c r="G96" s="13">
-        <v>83</v>
+        <v>72</v>
       </c>
     </row>
     <row r="97" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -23238,7 +23238,7 @@
         <v>1089</v>
       </c>
       <c r="G97" s="13">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="98" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -23261,7 +23261,7 @@
         <v>1089</v>
       </c>
       <c r="G98" s="13">
-        <v>69</v>
+        <v>39</v>
       </c>
     </row>
     <row r="99" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -23284,7 +23284,7 @@
         <v>1089</v>
       </c>
       <c r="G99" s="13">
-        <v>94</v>
+        <v>83</v>
       </c>
     </row>
     <row r="100" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -23307,7 +23307,7 @@
         <v>1089</v>
       </c>
       <c r="G100" s="13">
-        <v>77</v>
+        <v>96</v>
       </c>
     </row>
     <row r="101" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -23330,7 +23330,7 @@
         <v>1089</v>
       </c>
       <c r="G101" s="13">
-        <v>52</v>
+        <v>72</v>
       </c>
     </row>
     <row r="102" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -23353,7 +23353,7 @@
         <v>1089</v>
       </c>
       <c r="G102" s="13">
-        <v>80</v>
+        <v>94</v>
       </c>
     </row>
     <row r="103" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -23376,7 +23376,7 @@
         <v>1089</v>
       </c>
       <c r="G103" s="13">
-        <v>92</v>
+        <v>41</v>
       </c>
     </row>
     <row r="104" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -23399,7 +23399,7 @@
         <v>1089</v>
       </c>
       <c r="G104" s="13">
-        <v>54</v>
+        <v>72</v>
       </c>
     </row>
     <row r="105" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -23422,7 +23422,7 @@
         <v>1089</v>
       </c>
       <c r="G105" s="13">
-        <v>75</v>
+        <v>66</v>
       </c>
     </row>
     <row r="106" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -23445,7 +23445,7 @@
         <v>1089</v>
       </c>
       <c r="G106" s="13">
-        <v>53</v>
+        <v>84</v>
       </c>
     </row>
     <row r="107" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -23468,7 +23468,7 @@
         <v>1089</v>
       </c>
       <c r="G107" s="13">
-        <v>41</v>
+        <v>71</v>
       </c>
     </row>
     <row r="108" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -23491,7 +23491,7 @@
         <v>1089</v>
       </c>
       <c r="G108" s="13">
-        <v>88</v>
+        <v>50</v>
       </c>
     </row>
     <row r="109" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -23514,7 +23514,7 @@
         <v>1089</v>
       </c>
       <c r="G109" s="13">
-        <v>89</v>
+        <v>51</v>
       </c>
     </row>
     <row r="110" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -23537,7 +23537,7 @@
         <v>1089</v>
       </c>
       <c r="G110" s="13">
-        <v>85</v>
+        <v>35</v>
       </c>
     </row>
     <row r="111" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -23560,7 +23560,7 @@
         <v>1089</v>
       </c>
       <c r="G111" s="13">
-        <v>92</v>
+        <v>47</v>
       </c>
     </row>
     <row r="112" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -23583,7 +23583,7 @@
         <v>1089</v>
       </c>
       <c r="G112" s="13">
-        <v>77</v>
+        <v>61</v>
       </c>
     </row>
     <row r="113" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -23606,7 +23606,7 @@
         <v>1089</v>
       </c>
       <c r="G113" s="13">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="114" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -23652,7 +23652,7 @@
         <v>1089</v>
       </c>
       <c r="G115" s="13">
-        <v>46</v>
+        <v>84</v>
       </c>
     </row>
     <row r="116" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -23675,7 +23675,7 @@
         <v>1089</v>
       </c>
       <c r="G116" s="13">
-        <v>51</v>
+        <v>99</v>
       </c>
     </row>
     <row r="117" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -23698,7 +23698,7 @@
         <v>1089</v>
       </c>
       <c r="G117" s="13">
-        <v>51</v>
+        <v>36</v>
       </c>
     </row>
     <row r="118" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -23721,7 +23721,7 @@
         <v>1089</v>
       </c>
       <c r="G118" s="13">
-        <v>41</v>
+        <v>55</v>
       </c>
     </row>
     <row r="119" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -23744,7 +23744,7 @@
         <v>1089</v>
       </c>
       <c r="G119" s="13">
-        <v>82</v>
+        <v>66</v>
       </c>
     </row>
     <row r="120" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -23767,7 +23767,7 @@
         <v>1089</v>
       </c>
       <c r="G120" s="13">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="121" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -23790,7 +23790,7 @@
         <v>1089</v>
       </c>
       <c r="G121" s="13">
-        <v>43</v>
+        <v>73</v>
       </c>
     </row>
     <row r="122" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -23813,7 +23813,7 @@
         <v>1089</v>
       </c>
       <c r="G122" s="13">
-        <v>67</v>
+        <v>89</v>
       </c>
     </row>
     <row r="123" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -23836,7 +23836,7 @@
         <v>1089</v>
       </c>
       <c r="G123" s="13">
-        <v>35</v>
+        <v>89</v>
       </c>
     </row>
     <row r="124" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -23859,7 +23859,7 @@
         <v>1089</v>
       </c>
       <c r="G124" s="13">
-        <v>46</v>
+        <v>50</v>
       </c>
     </row>
     <row r="125" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -23882,7 +23882,7 @@
         <v>1089</v>
       </c>
       <c r="G125" s="13">
-        <v>71</v>
+        <v>43</v>
       </c>
     </row>
     <row r="126" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -23905,7 +23905,7 @@
         <v>1089</v>
       </c>
       <c r="G126" s="13">
-        <v>44</v>
+        <v>75</v>
       </c>
     </row>
     <row r="127" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -23928,7 +23928,7 @@
         <v>1089</v>
       </c>
       <c r="G127" s="13">
-        <v>79</v>
+        <v>86</v>
       </c>
     </row>
     <row r="128" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -23951,7 +23951,7 @@
         <v>1089</v>
       </c>
       <c r="G128" s="13">
-        <v>84</v>
+        <v>47</v>
       </c>
     </row>
     <row r="129" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -23974,7 +23974,7 @@
         <v>1089</v>
       </c>
       <c r="G129" s="13">
-        <v>66</v>
+        <v>75</v>
       </c>
     </row>
     <row r="130" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -23997,7 +23997,7 @@
         <v>1089</v>
       </c>
       <c r="G130" s="13">
-        <v>68</v>
+        <v>46</v>
       </c>
     </row>
     <row r="131" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -24020,7 +24020,7 @@
         <v>1089</v>
       </c>
       <c r="G131" s="13">
-        <v>77</v>
+        <v>89</v>
       </c>
     </row>
     <row r="132" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -24043,7 +24043,7 @@
         <v>1089</v>
       </c>
       <c r="G132" s="13">
-        <v>53</v>
+        <v>45</v>
       </c>
     </row>
     <row r="133" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -24066,7 +24066,7 @@
         <v>1089</v>
       </c>
       <c r="G133" s="13">
-        <v>47</v>
+        <v>76</v>
       </c>
     </row>
     <row r="134" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -24089,7 +24089,7 @@
         <v>1089</v>
       </c>
       <c r="G134" s="13">
-        <v>92</v>
+        <v>68</v>
       </c>
     </row>
     <row r="135" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -24112,7 +24112,7 @@
         <v>1089</v>
       </c>
       <c r="G135" s="13">
-        <v>68</v>
+        <v>86</v>
       </c>
     </row>
     <row r="136" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -24135,7 +24135,7 @@
         <v>1089</v>
       </c>
       <c r="G136" s="13">
-        <v>64</v>
+        <v>83</v>
       </c>
     </row>
     <row r="137" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -24158,7 +24158,7 @@
         <v>1089</v>
       </c>
       <c r="G137" s="13">
-        <v>53</v>
+        <v>41</v>
       </c>
     </row>
     <row r="138" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -24181,7 +24181,7 @@
         <v>1089</v>
       </c>
       <c r="G138" s="13">
-        <v>38</v>
+        <v>89</v>
       </c>
     </row>
     <row r="139" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -24204,7 +24204,7 @@
         <v>1089</v>
       </c>
       <c r="G139" s="13">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="140" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -24227,7 +24227,7 @@
         <v>1089</v>
       </c>
       <c r="G140" s="13">
-        <v>90</v>
+        <v>68</v>
       </c>
     </row>
     <row r="141" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -24250,7 +24250,7 @@
         <v>1089</v>
       </c>
       <c r="G141" s="13">
-        <v>80</v>
+        <v>91</v>
       </c>
     </row>
     <row r="142" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -24273,7 +24273,7 @@
         <v>1089</v>
       </c>
       <c r="G142" s="13">
-        <v>52</v>
+        <v>43</v>
       </c>
     </row>
     <row r="143" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -24296,7 +24296,7 @@
         <v>1089</v>
       </c>
       <c r="G143" s="13">
-        <v>37</v>
+        <v>60</v>
       </c>
     </row>
     <row r="144" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -24319,7 +24319,7 @@
         <v>1089</v>
       </c>
       <c r="G144" s="13">
-        <v>57</v>
+        <v>51</v>
       </c>
     </row>
     <row r="145" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -24342,7 +24342,7 @@
         <v>1089</v>
       </c>
       <c r="G145" s="13">
-        <v>53</v>
+        <v>36</v>
       </c>
     </row>
     <row r="146" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -24365,7 +24365,7 @@
         <v>1089</v>
       </c>
       <c r="G146" s="13">
-        <v>64</v>
+        <v>85</v>
       </c>
     </row>
     <row r="147" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -24388,7 +24388,7 @@
         <v>1089</v>
       </c>
       <c r="G147" s="13">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
     <row r="148" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -24411,7 +24411,7 @@
         <v>1089</v>
       </c>
       <c r="G148" s="13">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="149" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -24434,7 +24434,7 @@
         <v>1089</v>
       </c>
       <c r="G149" s="13">
-        <v>38</v>
+        <v>60</v>
       </c>
     </row>
     <row r="150" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -24457,7 +24457,7 @@
         <v>1089</v>
       </c>
       <c r="G150" s="13">
-        <v>62</v>
+        <v>41</v>
       </c>
     </row>
     <row r="151" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -24480,7 +24480,7 @@
         <v>1089</v>
       </c>
       <c r="G151" s="13">
-        <v>84</v>
+        <v>41</v>
       </c>
     </row>
     <row r="152" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -24503,7 +24503,7 @@
         <v>1089</v>
       </c>
       <c r="G152" s="13">
-        <v>89</v>
+        <v>98</v>
       </c>
     </row>
     <row r="153" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -24526,7 +24526,7 @@
         <v>1089</v>
       </c>
       <c r="G153" s="13">
-        <v>75</v>
+        <v>78</v>
       </c>
     </row>
     <row r="154" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -24549,7 +24549,7 @@
         <v>1089</v>
       </c>
       <c r="G154" s="13">
-        <v>95</v>
+        <v>68</v>
       </c>
     </row>
     <row r="155" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -24572,7 +24572,7 @@
         <v>1089</v>
       </c>
       <c r="G155" s="13">
-        <v>81</v>
+        <v>51</v>
       </c>
     </row>
     <row r="156" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -24595,7 +24595,7 @@
         <v>1089</v>
       </c>
       <c r="G156" s="13">
-        <v>78</v>
+        <v>52</v>
       </c>
     </row>
     <row r="157" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -24618,7 +24618,7 @@
         <v>1089</v>
       </c>
       <c r="G157" s="13">
-        <v>90</v>
+        <v>47</v>
       </c>
     </row>
     <row r="158" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -24641,7 +24641,7 @@
         <v>1089</v>
       </c>
       <c r="G158" s="13">
-        <v>37</v>
+        <v>66</v>
       </c>
     </row>
     <row r="159" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -24664,7 +24664,7 @@
         <v>1089</v>
       </c>
       <c r="G159" s="13">
-        <v>94</v>
+        <v>83</v>
       </c>
     </row>
     <row r="160" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -24687,7 +24687,7 @@
         <v>1089</v>
       </c>
       <c r="G160" s="13">
-        <v>41</v>
+        <v>48</v>
       </c>
     </row>
     <row r="161" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -24710,7 +24710,7 @@
         <v>1089</v>
       </c>
       <c r="G161" s="13">
-        <v>75</v>
+        <v>47</v>
       </c>
     </row>
     <row r="162" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -24733,7 +24733,7 @@
         <v>1089</v>
       </c>
       <c r="G162" s="13">
-        <v>80</v>
+        <v>71</v>
       </c>
     </row>
     <row r="163" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -24756,7 +24756,7 @@
         <v>1089</v>
       </c>
       <c r="G163" s="13">
-        <v>35</v>
+        <v>70</v>
       </c>
     </row>
     <row r="164" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -24779,7 +24779,7 @@
         <v>1089</v>
       </c>
       <c r="G164" s="13">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="165" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -24802,7 +24802,7 @@
         <v>1089</v>
       </c>
       <c r="G165" s="13">
-        <v>37</v>
+        <v>97</v>
       </c>
     </row>
     <row r="166" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -24825,7 +24825,7 @@
         <v>1089</v>
       </c>
       <c r="G166" s="13">
-        <v>47</v>
+        <v>87</v>
       </c>
     </row>
     <row r="167" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -24848,7 +24848,7 @@
         <v>1089</v>
       </c>
       <c r="G167" s="13">
-        <v>63</v>
+        <v>57</v>
       </c>
     </row>
     <row r="168" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -24871,7 +24871,7 @@
         <v>1089</v>
       </c>
       <c r="G168" s="13">
-        <v>72</v>
+        <v>53</v>
       </c>
     </row>
     <row r="169" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -24894,7 +24894,7 @@
         <v>1089</v>
       </c>
       <c r="G169" s="13">
-        <v>95</v>
+        <v>82</v>
       </c>
     </row>
     <row r="170" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -24917,7 +24917,7 @@
         <v>1089</v>
       </c>
       <c r="G170" s="13">
-        <v>93</v>
+        <v>47</v>
       </c>
     </row>
     <row r="171" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -24940,7 +24940,7 @@
         <v>1089</v>
       </c>
       <c r="G171" s="13">
-        <v>53</v>
+        <v>88</v>
       </c>
     </row>
     <row r="172" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -24963,7 +24963,7 @@
         <v>1089</v>
       </c>
       <c r="G172" s="13">
-        <v>92</v>
+        <v>86</v>
       </c>
     </row>
     <row r="173" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -24986,7 +24986,7 @@
         <v>1089</v>
       </c>
       <c r="G173" s="13">
-        <v>99</v>
+        <v>88</v>
       </c>
     </row>
     <row r="174" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -25009,7 +25009,7 @@
         <v>1089</v>
       </c>
       <c r="G174" s="13">
-        <v>66</v>
+        <v>81</v>
       </c>
     </row>
     <row r="175" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -25032,7 +25032,7 @@
         <v>1089</v>
       </c>
       <c r="G175" s="13">
-        <v>39</v>
+        <v>49</v>
       </c>
     </row>
     <row r="176" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -25055,7 +25055,7 @@
         <v>1089</v>
       </c>
       <c r="G176" s="13">
-        <v>45</v>
+        <v>91</v>
       </c>
     </row>
     <row r="177" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -25078,7 +25078,7 @@
         <v>1089</v>
       </c>
       <c r="G177" s="13">
-        <v>94</v>
+        <v>97</v>
       </c>
     </row>
     <row r="178" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -25101,7 +25101,7 @@
         <v>1089</v>
       </c>
       <c r="G178" s="13">
-        <v>91</v>
+        <v>59</v>
       </c>
     </row>
     <row r="179" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -25124,7 +25124,7 @@
         <v>1089</v>
       </c>
       <c r="G179" s="13">
-        <v>36</v>
+        <v>79</v>
       </c>
     </row>
     <row r="180" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -25147,7 +25147,7 @@
         <v>1089</v>
       </c>
       <c r="G180" s="13">
-        <v>99</v>
+        <v>71</v>
       </c>
     </row>
     <row r="181" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -25170,7 +25170,7 @@
         <v>1089</v>
       </c>
       <c r="G181" s="13">
-        <v>88</v>
+        <v>70</v>
       </c>
     </row>
     <row r="182" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -25193,7 +25193,7 @@
         <v>1089</v>
       </c>
       <c r="G182" s="13">
-        <v>62</v>
+        <v>37</v>
       </c>
     </row>
     <row r="183" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -25216,7 +25216,7 @@
         <v>1089</v>
       </c>
       <c r="G183" s="13">
-        <v>37</v>
+        <v>76</v>
       </c>
     </row>
     <row r="184" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -25239,7 +25239,7 @@
         <v>1089</v>
       </c>
       <c r="G184" s="13">
-        <v>97</v>
+        <v>57</v>
       </c>
     </row>
     <row r="185" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -25262,7 +25262,7 @@
         <v>1089</v>
       </c>
       <c r="G185" s="13">
-        <v>46</v>
+        <v>37</v>
       </c>
     </row>
     <row r="186" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -25285,7 +25285,7 @@
         <v>1089</v>
       </c>
       <c r="G186" s="13">
-        <v>70</v>
+        <v>57</v>
       </c>
     </row>
     <row r="187" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -25308,7 +25308,7 @@
         <v>1089</v>
       </c>
       <c r="G187" s="13">
-        <v>83</v>
+        <v>96</v>
       </c>
     </row>
     <row r="188" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -25354,7 +25354,7 @@
         <v>1089</v>
       </c>
       <c r="G189" s="13">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="190" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -25377,7 +25377,7 @@
         <v>1089</v>
       </c>
       <c r="G190" s="13">
-        <v>45</v>
+        <v>90</v>
       </c>
     </row>
     <row r="191" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -25400,7 +25400,7 @@
         <v>1089</v>
       </c>
       <c r="G191" s="13">
-        <v>87</v>
+        <v>63</v>
       </c>
     </row>
     <row r="192" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -25423,7 +25423,7 @@
         <v>1089</v>
       </c>
       <c r="G192" s="13">
-        <v>54</v>
+        <v>39</v>
       </c>
     </row>
     <row r="193" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -25446,7 +25446,7 @@
         <v>1089</v>
       </c>
       <c r="G193" s="13">
-        <v>92</v>
+        <v>43</v>
       </c>
     </row>
     <row r="194" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -25469,7 +25469,7 @@
         <v>1089</v>
       </c>
       <c r="G194" s="13">
-        <v>64</v>
+        <v>90</v>
       </c>
     </row>
     <row r="195" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -25492,7 +25492,7 @@
         <v>1089</v>
       </c>
       <c r="G195" s="13">
-        <v>50</v>
+        <v>43</v>
       </c>
     </row>
     <row r="196" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -25515,7 +25515,7 @@
         <v>1089</v>
       </c>
       <c r="G196" s="13">
-        <v>65</v>
+        <v>90</v>
       </c>
     </row>
     <row r="197" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -25538,7 +25538,7 @@
         <v>1089</v>
       </c>
       <c r="G197" s="13">
-        <v>66</v>
+        <v>55</v>
       </c>
     </row>
     <row r="198" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -25561,7 +25561,7 @@
         <v>1089</v>
       </c>
       <c r="G198" s="13">
-        <v>75</v>
+        <v>68</v>
       </c>
     </row>
     <row r="199" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -25584,7 +25584,7 @@
         <v>1089</v>
       </c>
       <c r="G199" s="13">
-        <v>54</v>
+        <v>42</v>
       </c>
     </row>
     <row r="200" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -25607,7 +25607,7 @@
         <v>1089</v>
       </c>
       <c r="G200" s="13">
-        <v>42</v>
+        <v>78</v>
       </c>
     </row>
     <row r="201" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -25653,7 +25653,7 @@
         <v>1089</v>
       </c>
       <c r="G202" s="13">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="203" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -25676,7 +25676,7 @@
         <v>1089</v>
       </c>
       <c r="G203" s="13">
-        <v>98</v>
+        <v>35</v>
       </c>
     </row>
     <row r="204" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -25699,7 +25699,7 @@
         <v>1089</v>
       </c>
       <c r="G204" s="13">
-        <v>39</v>
+        <v>75</v>
       </c>
     </row>
     <row r="205" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -25722,7 +25722,7 @@
         <v>1089</v>
       </c>
       <c r="G205" s="13">
-        <v>78</v>
+        <v>47</v>
       </c>
     </row>
     <row r="206" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -25745,7 +25745,7 @@
         <v>1089</v>
       </c>
       <c r="G206" s="13">
-        <v>74</v>
+        <v>95</v>
       </c>
     </row>
     <row r="207" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -25768,7 +25768,7 @@
         <v>1089</v>
       </c>
       <c r="G207" s="13">
-        <v>68</v>
+        <v>92</v>
       </c>
     </row>
     <row r="208" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -25791,7 +25791,7 @@
         <v>1089</v>
       </c>
       <c r="G208" s="13">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
     <row r="209" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -25814,7 +25814,7 @@
         <v>1089</v>
       </c>
       <c r="G209" s="13">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="210" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -25837,7 +25837,7 @@
         <v>1089</v>
       </c>
       <c r="G210" s="13">
-        <v>89</v>
+        <v>96</v>
       </c>
     </row>
     <row r="211" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -25860,7 +25860,7 @@
         <v>1089</v>
       </c>
       <c r="G211" s="13">
-        <v>53</v>
+        <v>60</v>
       </c>
     </row>
     <row r="212" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -25883,7 +25883,7 @@
         <v>1089</v>
       </c>
       <c r="G212" s="13">
-        <v>89</v>
+        <v>45</v>
       </c>
     </row>
     <row r="213" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -25906,7 +25906,7 @@
         <v>1089</v>
       </c>
       <c r="G213" s="13">
-        <v>41</v>
+        <v>88</v>
       </c>
     </row>
     <row r="214" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -25929,7 +25929,7 @@
         <v>1089</v>
       </c>
       <c r="G214" s="13">
-        <v>89</v>
+        <v>97</v>
       </c>
     </row>
     <row r="215" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -25952,7 +25952,7 @@
         <v>1089</v>
       </c>
       <c r="G215" s="13">
-        <v>84</v>
+        <v>60</v>
       </c>
     </row>
     <row r="216" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -25975,7 +25975,7 @@
         <v>1089</v>
       </c>
       <c r="G216" s="13">
-        <v>68</v>
+        <v>85</v>
       </c>
     </row>
     <row r="217" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -25998,7 +25998,7 @@
         <v>1089</v>
       </c>
       <c r="G217" s="13">
-        <v>38</v>
+        <v>66</v>
       </c>
     </row>
     <row r="218" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -26021,7 +26021,7 @@
         <v>1089</v>
       </c>
       <c r="G218" s="13">
-        <v>49</v>
+        <v>76</v>
       </c>
     </row>
     <row r="219" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -26044,7 +26044,7 @@
         <v>1089</v>
       </c>
       <c r="G219" s="13">
-        <v>94</v>
+        <v>76</v>
       </c>
     </row>
     <row r="220" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -26067,7 +26067,7 @@
         <v>1089</v>
       </c>
       <c r="G220" s="13">
-        <v>42</v>
+        <v>84</v>
       </c>
     </row>
     <row r="221" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -26090,7 +26090,7 @@
         <v>1089</v>
       </c>
       <c r="G221" s="13">
-        <v>44</v>
+        <v>81</v>
       </c>
     </row>
     <row r="222" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -26113,7 +26113,7 @@
         <v>1089</v>
       </c>
       <c r="G222" s="13">
-        <v>96</v>
+        <v>90</v>
       </c>
     </row>
     <row r="223" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -26136,7 +26136,7 @@
         <v>1089</v>
       </c>
       <c r="G223" s="13">
-        <v>65</v>
+        <v>97</v>
       </c>
     </row>
     <row r="224" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -26159,7 +26159,7 @@
         <v>1089</v>
       </c>
       <c r="G224" s="13">
-        <v>71</v>
+        <v>97</v>
       </c>
     </row>
     <row r="225" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -26182,7 +26182,7 @@
         <v>1089</v>
       </c>
       <c r="G225" s="13">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="226" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -26205,7 +26205,7 @@
         <v>1089</v>
       </c>
       <c r="G226" s="13">
-        <v>61</v>
+        <v>77</v>
       </c>
     </row>
     <row r="227" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -26228,7 +26228,7 @@
         <v>1089</v>
       </c>
       <c r="G227" s="13">
-        <v>38</v>
+        <v>74</v>
       </c>
     </row>
     <row r="228" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -26251,7 +26251,7 @@
         <v>1089</v>
       </c>
       <c r="G228" s="13">
-        <v>73</v>
+        <v>93</v>
       </c>
     </row>
     <row r="229" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -26274,7 +26274,7 @@
         <v>1089</v>
       </c>
       <c r="G229" s="13">
-        <v>41</v>
+        <v>49</v>
       </c>
     </row>
     <row r="230" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -26297,7 +26297,7 @@
         <v>1089</v>
       </c>
       <c r="G230" s="13">
-        <v>49</v>
+        <v>80</v>
       </c>
     </row>
     <row r="231" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -26320,7 +26320,7 @@
         <v>1089</v>
       </c>
       <c r="G231" s="13">
-        <v>39</v>
+        <v>99</v>
       </c>
     </row>
     <row r="232" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -26343,7 +26343,7 @@
         <v>1089</v>
       </c>
       <c r="G232" s="13">
-        <v>79</v>
+        <v>46</v>
       </c>
     </row>
     <row r="233" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -26366,7 +26366,7 @@
         <v>1089</v>
       </c>
       <c r="G233" s="13">
-        <v>87</v>
+        <v>76</v>
       </c>
     </row>
     <row r="234" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -26389,7 +26389,7 @@
         <v>1089</v>
       </c>
       <c r="G234" s="13">
-        <v>38</v>
+        <v>84</v>
       </c>
     </row>
     <row r="235" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -26412,7 +26412,7 @@
         <v>1089</v>
       </c>
       <c r="G235" s="13">
-        <v>93</v>
+        <v>71</v>
       </c>
     </row>
     <row r="236" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -26435,7 +26435,7 @@
         <v>1089</v>
       </c>
       <c r="G236" s="13">
-        <v>67</v>
+        <v>43</v>
       </c>
     </row>
     <row r="237" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -26458,7 +26458,7 @@
         <v>1089</v>
       </c>
       <c r="G237" s="13">
-        <v>52</v>
+        <v>59</v>
       </c>
     </row>
     <row r="238" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -26481,7 +26481,7 @@
         <v>1089</v>
       </c>
       <c r="G238" s="13">
-        <v>39</v>
+        <v>45</v>
       </c>
     </row>
     <row r="239" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -26504,7 +26504,7 @@
         <v>1089</v>
       </c>
       <c r="G239" s="13">
-        <v>68</v>
+        <v>43</v>
       </c>
     </row>
     <row r="240" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -26527,7 +26527,7 @@
         <v>1089</v>
       </c>
       <c r="G240" s="13">
-        <v>57</v>
+        <v>37</v>
       </c>
     </row>
     <row r="241" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -26550,7 +26550,7 @@
         <v>1089</v>
       </c>
       <c r="G241" s="13">
-        <v>90</v>
+        <v>69</v>
       </c>
     </row>
     <row r="242" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -26573,7 +26573,7 @@
         <v>1089</v>
       </c>
       <c r="G242" s="13">
-        <v>94</v>
+        <v>82</v>
       </c>
     </row>
     <row r="243" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -26596,7 +26596,7 @@
         <v>1089</v>
       </c>
       <c r="G243" s="13">
-        <v>76</v>
+        <v>63</v>
       </c>
     </row>
     <row r="244" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -26619,7 +26619,7 @@
         <v>1089</v>
       </c>
       <c r="G244" s="13">
-        <v>37</v>
+        <v>76</v>
       </c>
     </row>
     <row r="245" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -26642,7 +26642,7 @@
         <v>1089</v>
       </c>
       <c r="G245" s="13">
-        <v>88</v>
+        <v>91</v>
       </c>
     </row>
     <row r="246" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -26665,7 +26665,7 @@
         <v>1089</v>
       </c>
       <c r="G246" s="13">
-        <v>59</v>
+        <v>85</v>
       </c>
     </row>
     <row r="247" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -26688,7 +26688,7 @@
         <v>1089</v>
       </c>
       <c r="G247" s="13">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="248" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -26711,7 +26711,7 @@
         <v>1089</v>
       </c>
       <c r="G248" s="13">
-        <v>76</v>
+        <v>58</v>
       </c>
     </row>
     <row r="249" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -26734,7 +26734,7 @@
         <v>1089</v>
       </c>
       <c r="G249" s="13">
-        <v>78</v>
+        <v>46</v>
       </c>
     </row>
     <row r="250" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -26757,7 +26757,7 @@
         <v>1089</v>
       </c>
       <c r="G250" s="13">
-        <v>42</v>
+        <v>62</v>
       </c>
     </row>
     <row r="251" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -26780,7 +26780,7 @@
         <v>1089</v>
       </c>
       <c r="G251" s="13">
-        <v>51</v>
+        <v>74</v>
       </c>
     </row>
     <row r="252" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -26803,7 +26803,7 @@
         <v>1089</v>
       </c>
       <c r="G252" s="13">
-        <v>97</v>
+        <v>66</v>
       </c>
     </row>
     <row r="253" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -26826,7 +26826,7 @@
         <v>1089</v>
       </c>
       <c r="G253" s="13">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="254" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -26849,7 +26849,7 @@
         <v>1089</v>
       </c>
       <c r="G254" s="13">
-        <v>44</v>
+        <v>60</v>
       </c>
     </row>
     <row r="255" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -26872,7 +26872,7 @@
         <v>1089</v>
       </c>
       <c r="G255" s="13">
-        <v>94</v>
+        <v>40</v>
       </c>
     </row>
     <row r="256" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -26895,7 +26895,7 @@
         <v>1089</v>
       </c>
       <c r="G256" s="13">
-        <v>91</v>
+        <v>56</v>
       </c>
     </row>
     <row r="257" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -26918,7 +26918,7 @@
         <v>1089</v>
       </c>
       <c r="G257" s="13">
-        <v>93</v>
+        <v>80</v>
       </c>
     </row>
     <row r="258" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -26941,7 +26941,7 @@
         <v>1089</v>
       </c>
       <c r="G258" s="13">
-        <v>91</v>
+        <v>76</v>
       </c>
     </row>
     <row r="259" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -26964,7 +26964,7 @@
         <v>1089</v>
       </c>
       <c r="G259" s="13">
-        <v>78</v>
+        <v>44</v>
       </c>
     </row>
     <row r="260" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -26987,7 +26987,7 @@
         <v>1089</v>
       </c>
       <c r="G260" s="13">
-        <v>61</v>
+        <v>67</v>
       </c>
     </row>
     <row r="261" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -27010,7 +27010,7 @@
         <v>1089</v>
       </c>
       <c r="G261" s="13">
-        <v>91</v>
+        <v>94</v>
       </c>
     </row>
     <row r="262" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -27033,7 +27033,7 @@
         <v>1089</v>
       </c>
       <c r="G262" s="13">
-        <v>72</v>
+        <v>40</v>
       </c>
     </row>
     <row r="263" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -27056,7 +27056,7 @@
         <v>1089</v>
       </c>
       <c r="G263" s="13">
-        <v>46</v>
+        <v>88</v>
       </c>
     </row>
     <row r="264" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -27079,7 +27079,7 @@
         <v>1089</v>
       </c>
       <c r="G264" s="13">
-        <v>68</v>
+        <v>64</v>
       </c>
     </row>
     <row r="265" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -27102,7 +27102,7 @@
         <v>1089</v>
       </c>
       <c r="G265" s="13">
-        <v>89</v>
+        <v>78</v>
       </c>
     </row>
     <row r="266" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -27125,7 +27125,7 @@
         <v>1089</v>
       </c>
       <c r="G266" s="13">
-        <v>99</v>
+        <v>56</v>
       </c>
     </row>
     <row r="267" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -27148,7 +27148,7 @@
         <v>1089</v>
       </c>
       <c r="G267" s="13">
-        <v>79</v>
+        <v>44</v>
       </c>
     </row>
     <row r="268" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -27171,7 +27171,7 @@
         <v>1089</v>
       </c>
       <c r="G268" s="13">
-        <v>49</v>
+        <v>93</v>
       </c>
     </row>
     <row r="269" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -27194,7 +27194,7 @@
         <v>1089</v>
       </c>
       <c r="G269" s="13">
-        <v>83</v>
+        <v>96</v>
       </c>
     </row>
     <row r="270" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -27217,7 +27217,7 @@
         <v>1089</v>
       </c>
       <c r="G270" s="13">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="271" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -27240,7 +27240,7 @@
         <v>1089</v>
       </c>
       <c r="G271" s="13">
-        <v>89</v>
+        <v>75</v>
       </c>
     </row>
     <row r="272" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -27263,7 +27263,7 @@
         <v>1089</v>
       </c>
       <c r="G272" s="13">
-        <v>71</v>
+        <v>48</v>
       </c>
     </row>
     <row r="273" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -27286,7 +27286,7 @@
         <v>1089</v>
       </c>
       <c r="G273" s="13">
-        <v>59</v>
+        <v>44</v>
       </c>
     </row>
     <row r="274" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -27309,7 +27309,7 @@
         <v>1089</v>
       </c>
       <c r="G274" s="13">
-        <v>85</v>
+        <v>80</v>
       </c>
     </row>
     <row r="275" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -27332,7 +27332,7 @@
         <v>1089</v>
       </c>
       <c r="G275" s="13">
-        <v>68</v>
+        <v>57</v>
       </c>
     </row>
     <row r="276" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -27355,7 +27355,7 @@
         <v>1089</v>
       </c>
       <c r="G276" s="13">
-        <v>71</v>
+        <v>88</v>
       </c>
     </row>
     <row r="277" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -27378,7 +27378,7 @@
         <v>1089</v>
       </c>
       <c r="G277" s="13">
-        <v>59</v>
+        <v>70</v>
       </c>
     </row>
     <row r="278" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -27401,7 +27401,7 @@
         <v>1089</v>
       </c>
       <c r="G278" s="13">
-        <v>82</v>
+        <v>87</v>
       </c>
     </row>
     <row r="279" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -27424,7 +27424,7 @@
         <v>1089</v>
       </c>
       <c r="G279" s="13">
-        <v>62</v>
+        <v>55</v>
       </c>
     </row>
     <row r="280" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -27447,7 +27447,7 @@
         <v>1089</v>
       </c>
       <c r="G280" s="13">
-        <v>80</v>
+        <v>75</v>
       </c>
     </row>
     <row r="281" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -27470,7 +27470,7 @@
         <v>1089</v>
       </c>
       <c r="G281" s="13">
-        <v>48</v>
+        <v>61</v>
       </c>
     </row>
     <row r="282" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -27516,7 +27516,7 @@
         <v>1089</v>
       </c>
       <c r="G283" s="13">
-        <v>69</v>
+        <v>77</v>
       </c>
     </row>
     <row r="284" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -27562,7 +27562,7 @@
         <v>1089</v>
       </c>
       <c r="G285" s="13">
-        <v>50</v>
+        <v>37</v>
       </c>
     </row>
     <row r="286" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -27585,7 +27585,7 @@
         <v>1089</v>
       </c>
       <c r="G286" s="13">
-        <v>89</v>
+        <v>44</v>
       </c>
     </row>
     <row r="287" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -27608,7 +27608,7 @@
         <v>1089</v>
       </c>
       <c r="G287" s="13">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="288" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -27631,7 +27631,7 @@
         <v>1089</v>
       </c>
       <c r="G288" s="13">
-        <v>84</v>
+        <v>71</v>
       </c>
     </row>
     <row r="289" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -27677,7 +27677,7 @@
         <v>1089</v>
       </c>
       <c r="G290" s="13">
-        <v>39</v>
+        <v>42</v>
       </c>
     </row>
     <row r="291" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -27700,7 +27700,7 @@
         <v>1089</v>
       </c>
       <c r="G291" s="13">
-        <v>99</v>
+        <v>92</v>
       </c>
     </row>
     <row r="292" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -27723,7 +27723,7 @@
         <v>1089</v>
       </c>
       <c r="G292" s="13">
-        <v>86</v>
+        <v>37</v>
       </c>
     </row>
     <row r="293" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -27746,7 +27746,7 @@
         <v>1089</v>
       </c>
       <c r="G293" s="13">
-        <v>79</v>
+        <v>51</v>
       </c>
     </row>
     <row r="294" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -27769,7 +27769,7 @@
         <v>1089</v>
       </c>
       <c r="G294" s="13">
-        <v>49</v>
+        <v>79</v>
       </c>
     </row>
     <row r="295" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -27792,7 +27792,7 @@
         <v>1089</v>
       </c>
       <c r="G295" s="13">
-        <v>95</v>
+        <v>65</v>
       </c>
     </row>
     <row r="296" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -27815,7 +27815,7 @@
         <v>1089</v>
       </c>
       <c r="G296" s="13">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="297" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -27838,7 +27838,7 @@
         <v>1089</v>
       </c>
       <c r="G297" s="13">
-        <v>47</v>
+        <v>72</v>
       </c>
     </row>
     <row r="298" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -27861,7 +27861,7 @@
         <v>1089</v>
       </c>
       <c r="G298" s="13">
-        <v>45</v>
+        <v>58</v>
       </c>
     </row>
     <row r="299" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -27884,7 +27884,7 @@
         <v>1089</v>
       </c>
       <c r="G299" s="13">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="300" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -27907,7 +27907,7 @@
         <v>1089</v>
       </c>
       <c r="G300" s="13">
-        <v>65</v>
+        <v>54</v>
       </c>
     </row>
     <row r="301" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -27930,7 +27930,7 @@
         <v>1089</v>
       </c>
       <c r="G301" s="13">
-        <v>68</v>
+        <v>77</v>
       </c>
     </row>
     <row r="302" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -27953,7 +27953,7 @@
         <v>1089</v>
       </c>
       <c r="G302" s="13">
-        <v>98</v>
+        <v>40</v>
       </c>
     </row>
     <row r="303" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -27976,7 +27976,7 @@
         <v>1089</v>
       </c>
       <c r="G303" s="13">
-        <v>88</v>
+        <v>85</v>
       </c>
     </row>
     <row r="304" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -27999,7 +27999,7 @@
         <v>1089</v>
       </c>
       <c r="G304" s="13">
-        <v>60</v>
+        <v>88</v>
       </c>
     </row>
     <row r="305" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -28022,7 +28022,7 @@
         <v>1089</v>
       </c>
       <c r="G305" s="13">
-        <v>96</v>
+        <v>42</v>
       </c>
     </row>
     <row r="306" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -28045,7 +28045,7 @@
         <v>1089</v>
       </c>
       <c r="G306" s="13">
-        <v>60</v>
+        <v>45</v>
       </c>
     </row>
     <row r="307" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -28068,7 +28068,7 @@
         <v>1089</v>
       </c>
       <c r="G307" s="13">
-        <v>67</v>
+        <v>46</v>
       </c>
     </row>
     <row r="308" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -28091,7 +28091,7 @@
         <v>1089</v>
       </c>
       <c r="G308" s="13">
-        <v>71</v>
+        <v>49</v>
       </c>
     </row>
     <row r="309" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -28114,7 +28114,7 @@
         <v>1089</v>
       </c>
       <c r="G309" s="13">
-        <v>76</v>
+        <v>46</v>
       </c>
     </row>
     <row r="310" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -28137,7 +28137,7 @@
         <v>1089</v>
       </c>
       <c r="G310" s="13">
-        <v>59</v>
+        <v>64</v>
       </c>
     </row>
     <row r="311" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -28160,7 +28160,7 @@
         <v>1089</v>
       </c>
       <c r="G311" s="13">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="312" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -28183,7 +28183,7 @@
         <v>1089</v>
       </c>
       <c r="G312" s="13">
-        <v>77</v>
+        <v>66</v>
       </c>
     </row>
     <row r="313" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -28206,7 +28206,7 @@
         <v>1089</v>
       </c>
       <c r="G313" s="13">
-        <v>36</v>
+        <v>44</v>
       </c>
     </row>
     <row r="314" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -28229,7 +28229,7 @@
         <v>1089</v>
       </c>
       <c r="G314" s="13">
-        <v>95</v>
+        <v>69</v>
       </c>
     </row>
     <row r="315" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -28252,7 +28252,7 @@
         <v>1089</v>
       </c>
       <c r="G315" s="13">
-        <v>54</v>
+        <v>41</v>
       </c>
     </row>
     <row r="316" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -28275,7 +28275,7 @@
         <v>1089</v>
       </c>
       <c r="G316" s="13">
-        <v>50</v>
+        <v>75</v>
       </c>
     </row>
     <row r="317" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -28298,7 +28298,7 @@
         <v>1089</v>
       </c>
       <c r="G317" s="13">
-        <v>97</v>
+        <v>53</v>
       </c>
     </row>
     <row r="318" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -28321,7 +28321,7 @@
         <v>1089</v>
       </c>
       <c r="G318" s="13">
-        <v>72</v>
+        <v>83</v>
       </c>
     </row>
     <row r="319" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -28344,7 +28344,7 @@
         <v>1089</v>
       </c>
       <c r="G319" s="13">
-        <v>71</v>
+        <v>57</v>
       </c>
     </row>
     <row r="320" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -28367,7 +28367,7 @@
         <v>1089</v>
       </c>
       <c r="G320" s="13">
-        <v>68</v>
+        <v>91</v>
       </c>
     </row>
     <row r="321" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -28390,7 +28390,7 @@
         <v>1089</v>
       </c>
       <c r="G321" s="13">
-        <v>50</v>
+        <v>59</v>
       </c>
     </row>
     <row r="322" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -28413,7 +28413,7 @@
         <v>1089</v>
       </c>
       <c r="G322" s="13">
-        <v>78</v>
+        <v>97</v>
       </c>
     </row>
     <row r="323" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -28436,7 +28436,7 @@
         <v>1089</v>
       </c>
       <c r="G323" s="13">
-        <v>88</v>
+        <v>75</v>
       </c>
     </row>
     <row r="324" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -28459,7 +28459,7 @@
         <v>1089</v>
       </c>
       <c r="G324" s="13">
-        <v>53</v>
+        <v>85</v>
       </c>
     </row>
     <row r="325" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -28482,7 +28482,7 @@
         <v>1089</v>
       </c>
       <c r="G325" s="13">
-        <v>40</v>
+        <v>46</v>
       </c>
     </row>
     <row r="326" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -28505,7 +28505,7 @@
         <v>1089</v>
       </c>
       <c r="G326" s="13">
-        <v>48</v>
+        <v>43</v>
       </c>
     </row>
     <row r="327" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -28528,7 +28528,7 @@
         <v>1089</v>
       </c>
       <c r="G327" s="13">
-        <v>91</v>
+        <v>37</v>
       </c>
     </row>
     <row r="328" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -28574,7 +28574,7 @@
         <v>1089</v>
       </c>
       <c r="G329" s="13">
-        <v>89</v>
+        <v>55</v>
       </c>
     </row>
     <row r="330" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -28597,7 +28597,7 @@
         <v>1089</v>
       </c>
       <c r="G330" s="13">
-        <v>47</v>
+        <v>82</v>
       </c>
     </row>
     <row r="331" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -28620,7 +28620,7 @@
         <v>1089</v>
       </c>
       <c r="G331" s="13">
-        <v>76</v>
+        <v>69</v>
       </c>
     </row>
     <row r="332" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -28643,7 +28643,7 @@
         <v>1089</v>
       </c>
       <c r="G332" s="13">
-        <v>77</v>
+        <v>93</v>
       </c>
     </row>
     <row r="333" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -28666,7 +28666,7 @@
         <v>1089</v>
       </c>
       <c r="G333" s="13">
-        <v>54</v>
+        <v>80</v>
       </c>
     </row>
     <row r="334" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -28689,7 +28689,7 @@
         <v>1089</v>
       </c>
       <c r="G334" s="13">
-        <v>73</v>
+        <v>85</v>
       </c>
     </row>
     <row r="335" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -28712,7 +28712,7 @@
         <v>1089</v>
       </c>
       <c r="G335" s="13">
-        <v>40</v>
+        <v>90</v>
       </c>
     </row>
     <row r="336" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -28735,7 +28735,7 @@
         <v>1089</v>
       </c>
       <c r="G336" s="13">
-        <v>89</v>
+        <v>71</v>
       </c>
     </row>
     <row r="337" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -28758,7 +28758,7 @@
         <v>1089</v>
       </c>
       <c r="G337" s="13">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="338" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -28781,7 +28781,7 @@
         <v>1089</v>
       </c>
       <c r="G338" s="13">
-        <v>85</v>
+        <v>37</v>
       </c>
     </row>
     <row r="339" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -28804,7 +28804,7 @@
         <v>1089</v>
       </c>
       <c r="G339" s="13">
-        <v>43</v>
+        <v>78</v>
       </c>
     </row>
     <row r="340" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -28827,7 +28827,7 @@
         <v>1089</v>
       </c>
       <c r="G340" s="13">
-        <v>41</v>
+        <v>83</v>
       </c>
     </row>
     <row r="341" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -28850,7 +28850,7 @@
         <v>1089</v>
       </c>
       <c r="G341" s="13">
-        <v>48</v>
+        <v>42</v>
       </c>
     </row>
     <row r="342" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -28873,7 +28873,7 @@
         <v>1089</v>
       </c>
       <c r="G342" s="13">
-        <v>53</v>
+        <v>59</v>
       </c>
     </row>
     <row r="343" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -28896,7 +28896,7 @@
         <v>1089</v>
       </c>
       <c r="G343" s="13">
-        <v>99</v>
+        <v>71</v>
       </c>
     </row>
     <row r="344" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -28919,7 +28919,7 @@
         <v>1089</v>
       </c>
       <c r="G344" s="13">
-        <v>94</v>
+        <v>36</v>
       </c>
     </row>
     <row r="345" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -28942,7 +28942,7 @@
         <v>1089</v>
       </c>
       <c r="G345" s="13">
-        <v>68</v>
+        <v>75</v>
       </c>
     </row>
     <row r="346" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -28965,7 +28965,7 @@
         <v>1089</v>
       </c>
       <c r="G346" s="13">
-        <v>81</v>
+        <v>42</v>
       </c>
     </row>
     <row r="347" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -28988,7 +28988,7 @@
         <v>1089</v>
       </c>
       <c r="G347" s="13">
-        <v>86</v>
+        <v>78</v>
       </c>
     </row>
     <row r="348" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -29011,7 +29011,7 @@
         <v>1089</v>
       </c>
       <c r="G348" s="13">
-        <v>93</v>
+        <v>45</v>
       </c>
     </row>
     <row r="349" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -29034,7 +29034,7 @@
         <v>1089</v>
       </c>
       <c r="G349" s="13">
-        <v>72</v>
+        <v>44</v>
       </c>
     </row>
     <row r="350" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -29057,7 +29057,7 @@
         <v>1089</v>
       </c>
       <c r="G350" s="13">
-        <v>46</v>
+        <v>52</v>
       </c>
     </row>
     <row r="351" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -29080,7 +29080,7 @@
         <v>1089</v>
       </c>
       <c r="G351" s="13">
-        <v>39</v>
+        <v>68</v>
       </c>
     </row>
     <row r="352" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -29103,7 +29103,7 @@
         <v>1089</v>
       </c>
       <c r="G352" s="13">
-        <v>44</v>
+        <v>80</v>
       </c>
     </row>
     <row r="353" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -29126,7 +29126,7 @@
         <v>1089</v>
       </c>
       <c r="G353" s="13">
-        <v>43</v>
+        <v>64</v>
       </c>
     </row>
     <row r="354" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -29149,7 +29149,7 @@
         <v>1089</v>
       </c>
       <c r="G354" s="13">
-        <v>73</v>
+        <v>53</v>
       </c>
     </row>
     <row r="355" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -29172,7 +29172,7 @@
         <v>1089</v>
       </c>
       <c r="G355" s="13">
-        <v>94</v>
+        <v>59</v>
       </c>
     </row>
     <row r="356" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -29195,7 +29195,7 @@
         <v>1089</v>
       </c>
       <c r="G356" s="13">
-        <v>52</v>
+        <v>58</v>
       </c>
     </row>
     <row r="357" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -29218,7 +29218,7 @@
         <v>1089</v>
       </c>
       <c r="G357" s="13">
-        <v>92</v>
+        <v>64</v>
       </c>
     </row>
     <row r="358" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -29241,7 +29241,7 @@
         <v>1089</v>
       </c>
       <c r="G358" s="13">
-        <v>95</v>
+        <v>79</v>
       </c>
     </row>
     <row r="359" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -29264,7 +29264,7 @@
         <v>1089</v>
       </c>
       <c r="G359" s="13">
-        <v>91</v>
+        <v>42</v>
       </c>
     </row>
     <row r="360" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -29287,7 +29287,7 @@
         <v>1089</v>
       </c>
       <c r="G360" s="13">
-        <v>64</v>
+        <v>95</v>
       </c>
     </row>
     <row r="361" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -29310,7 +29310,7 @@
         <v>1089</v>
       </c>
       <c r="G361" s="13">
-        <v>39</v>
+        <v>99</v>
       </c>
     </row>
   </sheetData>
